--- a/Задание/Задание ра разработку ППО для чтения данных Modbus.xlsx
+++ b/Задание/Задание ра разработку ППО для чтения данных Modbus.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20384"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED8D163A-6F1C-4EB2-8C97-A09ECC78ED8B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E99559E-F08B-4898-8F11-39F0960C7E96}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,12 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Задание ра разработку ППО для чтения данных Modbus и генерации данных для импорта</t>
-  </si>
-  <si>
-    <t>№</t>
   </si>
   <si>
     <t>Задание ра разработку ППО для чтения данных Modbus и генерации данных для импорта.
@@ -36,6 +33,48 @@
   </si>
   <si>
     <t>Запись кода в файлы (Windows PowerShell)</t>
+  </si>
+  <si>
+    <t>используя данные modbus необходимо генерить таблицу на основании шаблона Шаблон Modbus SCADA.</t>
+  </si>
+  <si>
+    <t>Марка формируется: _Имя подсистемы (заполняется на форме в ручную)_MB_ТИП(HR - Holding Register и т.п.)_RegisterType+Adress/bit_DataType( Word, Real, Bool, INT, UINT , UDINT,  в зависимости от Data Type).</t>
+  </si>
+  <si>
+    <t>Например _ASU_MB_HR_40023_REAL</t>
+  </si>
+  <si>
+    <t>Тип объекта: DataType</t>
+  </si>
+  <si>
+    <t>Наименование: MB_ТИП(HR - Holding Register и т.п.)_RegisterType+Adress/bit_DataType( Word, Real, Bool, INT, UINT , UDINT,  в зависимости от Data Type).</t>
+  </si>
+  <si>
+    <t>Номер: 0 (меняется на форме в ручную сразу для всех)</t>
+  </si>
+  <si>
+    <t>Период архив: 0 (меняется на форме в ручную сразу для всех)</t>
+  </si>
+  <si>
+    <t>Маска упр. в срезах: 1 (меняется на форме в ручную сразу для всех)</t>
+  </si>
+  <si>
+    <t>Классификатор: задается на форме текстом, по умолчанию: [ВСЕ]</t>
+  </si>
+  <si>
+    <t>Группа событий: задается на форме текстом, по умолчанию: [ВСЕ]</t>
+  </si>
+  <si>
+    <t>КОНТРОЛЛЕР:  задается на форме текстом, по умолчанию: ничего не заполнять</t>
+  </si>
+  <si>
+    <t>Адрес: RegisterType+ Adress/bit(формат: 40001, 30025 и т.д. )</t>
+  </si>
+  <si>
+    <t>№ ресурса или группа: RegisterType (1, 2, 3 или 4)</t>
+  </si>
+  <si>
+    <t>DataType может быть только 4 типов: WORD, REAL, BOOL, INT, UINT , UDINT. Добавь возможность присваиваеть типу данных в исходном файле и типу в DataType. Присваивание применяется сразу для всех однотипных данных.</t>
   </si>
 </sst>
 </file>
@@ -369,112 +408,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="85.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="199.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="2:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="150" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="5" spans="2:2" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+    <row r="22" spans="2:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B22" s="2" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
